--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>97567</v>
+        <v>98092</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>97567</v>
+        <v>98092</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>97567</v>
+        <v>98092</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,11 +794,6 @@
       </c>
       <c r="E3" t="n">
         <v>219790</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -882,7 +877,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,11 +891,6 @@
       </c>
       <c r="E4" t="n">
         <v>219790</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1095,7 +1085,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,11 +1099,6 @@
       </c>
       <c r="E6" t="n">
         <v>219790</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,6 +794,11 @@
       </c>
       <c r="E3" t="n">
         <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -877,7 +882,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,6 +896,11 @@
       </c>
       <c r="E4" t="n">
         <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1085,7 +1095,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,6 +1109,11 @@
       </c>
       <c r="E6" t="n">
         <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 50924-2023 artfynd.xlsx
+++ b/artfynd/A 50924-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966200</v>
       </c>
       <c r="B3" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>113966199</v>
       </c>
       <c r="B4" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>113966198</v>
       </c>
       <c r="B6" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
